--- a/tables/modelstats.xlsx
+++ b/tables/modelstats.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,17 +454,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rnn_lin1</t>
+          <t>rnn</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7766.914702763253</v>
+        <v>10880.60035108357</v>
       </c>
       <c r="E2" t="n">
-        <v>6570.6982421875</v>
+        <v>9062.7841796875</v>
       </c>
       <c r="F2" t="n">
-        <v>1.289363145828247</v>
+        <v>1.653098583221436</v>
       </c>
     </row>
     <row r="3">
@@ -478,17 +478,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gru_lin1</t>
+          <t>rnn_lin1</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6696.421133710155</v>
+        <v>7766.914702763253</v>
       </c>
       <c r="E3" t="n">
-        <v>5667.11962890625</v>
+        <v>6570.6982421875</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9034479856491089</v>
+        <v>1.289363145828247</v>
       </c>
     </row>
     <row r="4">
@@ -502,17 +502,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>gru1</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8246.469305102639</v>
+        <v>8784.831927817402</v>
       </c>
       <c r="E4" t="n">
-        <v>7374.9033203125</v>
+        <v>7156.763671875</v>
       </c>
       <c r="F4" t="n">
-        <v>1.281058430671692</v>
+        <v>1.430075407028198</v>
       </c>
     </row>
     <row r="5">
@@ -526,17 +526,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lstm_lin1</t>
+          <t>gru_lin1</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7314.216567753514</v>
+        <v>6696.421133710155</v>
       </c>
       <c r="E5" t="n">
-        <v>6742.97607421875</v>
+        <v>5667.11962890625</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0357825756073</v>
+        <v>0.9034479856491089</v>
       </c>
     </row>
     <row r="6">
@@ -550,17 +550,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lstm_comb</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9925.951440542111</v>
+        <v>8246.469305102639</v>
       </c>
       <c r="E6" t="n">
-        <v>8241.8759765625</v>
+        <v>7374.9033203125</v>
       </c>
       <c r="F6" t="n">
-        <v>1.565523266792297</v>
+        <v>1.281058430671692</v>
       </c>
     </row>
     <row r="7">
@@ -574,17 +574,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rnn_comb</t>
+          <t>lstm1</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10045.34797804436</v>
+        <v>12978.34873934277</v>
       </c>
       <c r="E7" t="n">
-        <v>8620.1552734375</v>
+        <v>11261.2451171875</v>
       </c>
       <c r="F7" t="n">
-        <v>1.504447937011719</v>
+        <v>2.009578704833984</v>
       </c>
     </row>
     <row r="8">
@@ -598,17 +598,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gru_comb</t>
+          <t>lstm_lin1</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8161.784608772765</v>
+        <v>7314.216567753514</v>
       </c>
       <c r="E8" t="n">
-        <v>6790.69580078125</v>
+        <v>6742.97607421875</v>
       </c>
       <c r="F8" t="n">
-        <v>1.246353149414062</v>
+        <v>1.0357825756073</v>
       </c>
     </row>
     <row r="9">
@@ -617,22 +617,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>24-25</t>
+          <t>23-24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>rnn_lin1</t>
+          <t>lstm_comb</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14953.06149255061</v>
+        <v>9925.951440542111</v>
       </c>
       <c r="E9" t="n">
-        <v>10603.04296875</v>
+        <v>8241.8759765625</v>
       </c>
       <c r="F9" t="n">
-        <v>1.232327342033386</v>
+        <v>1.565523266792297</v>
       </c>
     </row>
     <row r="10">
@@ -641,22 +641,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24-25</t>
+          <t>23-24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>gru_lin1</t>
+          <t>rnn_comb</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14868.26096085215</v>
+        <v>10045.34797804436</v>
       </c>
       <c r="E10" t="n">
-        <v>10005.2353515625</v>
+        <v>8620.1552734375</v>
       </c>
       <c r="F10" t="n">
-        <v>1.191045165061951</v>
+        <v>1.504447937011719</v>
       </c>
     </row>
     <row r="11">
@@ -665,22 +665,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>24-25</t>
+          <t>23-24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>gru_comb</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14002.27410101659</v>
+        <v>8161.784608772765</v>
       </c>
       <c r="E11" t="n">
-        <v>10143.234375</v>
+        <v>6790.69580078125</v>
       </c>
       <c r="F11" t="n">
-        <v>1.106807470321655</v>
+        <v>1.246353149414062</v>
       </c>
     </row>
     <row r="12">
@@ -694,17 +694,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>lstm_lin1</t>
+          <t>rnn</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17452.0068760014</v>
+        <v>15611.66435714014</v>
       </c>
       <c r="E12" t="n">
-        <v>14237.921875</v>
+        <v>10816.9052734375</v>
       </c>
       <c r="F12" t="n">
-        <v>1.367529153823853</v>
+        <v>0.9515868425369263</v>
       </c>
     </row>
     <row r="13">
@@ -718,17 +718,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>lstm_comb</t>
+          <t>rnn_lin1</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>20234.55737099282</v>
+        <v>14953.06149255061</v>
       </c>
       <c r="E13" t="n">
-        <v>14761.99609375</v>
+        <v>10603.04296875</v>
       </c>
       <c r="F13" t="n">
-        <v>1.540326952934265</v>
+        <v>1.232327342033386</v>
       </c>
     </row>
     <row r="14">
@@ -742,17 +742,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>rnn_comb</t>
+          <t>gru1</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>19980.33673389916</v>
+        <v>20468.28102210833</v>
       </c>
       <c r="E14" t="n">
-        <v>14755.59375</v>
+        <v>15297.5341796875</v>
       </c>
       <c r="F14" t="n">
-        <v>1.509582281112671</v>
+        <v>1.462140917778015</v>
       </c>
     </row>
     <row r="15">
@@ -766,17 +766,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gru_comb</t>
+          <t>gru_lin1</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17390.31270564161</v>
+        <v>14868.26096085215</v>
       </c>
       <c r="E15" t="n">
-        <v>13031.6845703125</v>
+        <v>10005.2353515625</v>
       </c>
       <c r="F15" t="n">
-        <v>1.397760391235352</v>
+        <v>1.191045165061951</v>
       </c>
     </row>
     <row r="16">
@@ -785,22 +785,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>25-26</t>
+          <t>24-25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rnn_lin1</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6474.919613400617</v>
+        <v>14002.27410101659</v>
       </c>
       <c r="E16" t="n">
-        <v>4726.44287109375</v>
+        <v>10143.234375</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5769714713096619</v>
+        <v>1.106807470321655</v>
       </c>
     </row>
     <row r="17">
@@ -809,22 +809,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>25-26</t>
+          <t>24-25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>gru_lin1</t>
+          <t>lstm1</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>9317.237788100076</v>
+        <v>25009.65317632374</v>
       </c>
       <c r="E17" t="n">
-        <v>6894.8740234375</v>
+        <v>18510.400390625</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8618780374526978</v>
+        <v>1.758995056152344</v>
       </c>
     </row>
     <row r="18">
@@ -833,22 +833,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>25-26</t>
+          <t>24-25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>lstm_lin1</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>9976.850805740256</v>
+        <v>17452.0068760014</v>
       </c>
       <c r="E18" t="n">
-        <v>7215.68310546875</v>
+        <v>14237.921875</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8016821146011353</v>
+        <v>1.367529153823853</v>
       </c>
     </row>
     <row r="19">
@@ -857,22 +857,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>25-26</t>
+          <t>24-25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>lstm_lin1</t>
+          <t>lstm_comb</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7182.379828441267</v>
+        <v>20234.55737099282</v>
       </c>
       <c r="E19" t="n">
-        <v>4799.2431640625</v>
+        <v>14761.99609375</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5642114281654358</v>
+        <v>1.540326952934265</v>
       </c>
     </row>
     <row r="20">
@@ -881,22 +881,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>25-26</t>
+          <t>24-25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>lstm_comb</t>
+          <t>rnn_comb</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>9625.078908767449</v>
+        <v>19980.33673389916</v>
       </c>
       <c r="E20" t="n">
-        <v>6103.51123046875</v>
+        <v>14755.59375</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5817875266075134</v>
+        <v>1.509582281112671</v>
       </c>
     </row>
     <row r="21">
@@ -905,22 +905,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>25-26</t>
+          <t>24-25</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rnn_comb</t>
+          <t>gru_comb</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>7574.696561579216</v>
+        <v>17390.31270564161</v>
       </c>
       <c r="E21" t="n">
-        <v>5910.89697265625</v>
+        <v>13031.6845703125</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7149050235748291</v>
+        <v>1.397760391235352</v>
       </c>
     </row>
     <row r="22">
@@ -934,16 +934,160 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>rnn_lin1</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>6474.919613400617</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4726.44287109375</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5769714713096619</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>gru_lin1</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>9317.237788100076</v>
+      </c>
+      <c r="E23" t="n">
+        <v>6894.8740234375</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.8618780374526978</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>lstm1</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>9445.520419754541</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6267.05517578125</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.873779296875</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>lstm_lin1</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>7182.379828441267</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4799.2431640625</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.5642114281654358</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>lstm_comb</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>9625.078908767449</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6103.51123046875</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.5817875266075134</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>rnn_comb</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>7574.696561579216</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5910.89697265625</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.7149050235748291</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>gru_comb</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D28" t="n">
         <v>8252.707676877935</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E28" t="n">
         <v>6194.099609375</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F28" t="n">
         <v>0.722800076007843</v>
       </c>
     </row>
